--- a/docs/testcases/goi-cuoc/web/TCs_GOICUOC_Quanlygoicuoc_UC1_UC2.xlsx
+++ b/docs/testcases/goi-cuoc/web/TCs_GOICUOC_Quanlygoicuoc_UC1_UC2.xlsx
@@ -3613,7 +3613,7 @@
       </c>
       <c r="E15" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị màn hình giống design gồm:
+          <t>1. Hiển thị màn hình giống design gồm:
 + Tiêu đề: Quản lý gói cước
 + Button Thêm gói cước
 + Ô tìm kiếm
@@ -3652,15 +3652,16 @@
       </c>
       <c r="D16" s="685" t="inlineStr">
         <is>
-          <t>Kiểm tra về bố cục, font chữ, chính tả, màu chữ</t>
+          <t>1. Kiểm tra về bố cục, font chữ, chính tả, màu chữ</t>
         </is>
       </c>
       <c r="E16" s="685" t="inlineStr">
         <is>
-          <t>1. Các label, có độ dài, rộng và khoảng cách bằng nhau, không xô lệch
-2. Các label sử dụng cùng 1 loại font, cỡ chữ, căn lề
-3. Kiểm tra tất cả lỗi về chính tả, cấu trúc câu, ngữ pháp trên màn hình
-4. Form được bố trí hợp lý và dễ sử dụng</t>
+          <t>1. 
+- Các label, có độ dài, rộng và khoảng cách bằng nhau, không xô lệch
+- Các label sử dụng cùng 1 loại font, cỡ chữ, căn lề
+- Kiểm tra tất cả lỗi về chính tả, cấu trúc câu, ngữ pháp trên màn hình
+- Form được bố trí hợp lý và dễ sử dụng</t>
         </is>
       </c>
       <c r="F16" s="683" t="n"/>
@@ -3689,12 +3690,12 @@
       </c>
       <c r="D17" s="685" t="inlineStr">
         <is>
-          <t>Nhấn Tab liên tục</t>
+          <t>1. Nhấn Tab liên tục</t>
         </is>
       </c>
       <c r="E17" s="685" t="inlineStr">
         <is>
-          <t>Con trỏ di chuyển lần lượt theo thứ tự: Từ trái qua phải, từ trên xuống dưới</t>
+          <t>1. Con trỏ di chuyển lần lượt theo thứ tự: Từ trái qua phải, từ trên xuống dưới</t>
         </is>
       </c>
       <c r="F17" s="683" t="n"/>
@@ -3723,12 +3724,12 @@
       </c>
       <c r="D18" s="685" t="inlineStr">
         <is>
-          <t>Nhấn phím Shift-Tab liên tục</t>
+          <t>1. Nhấn phím Shift-Tab liên tục</t>
         </is>
       </c>
       <c r="E18" s="685" t="inlineStr">
         <is>
-          <t>Con trỏ di chuyển ngược lại theo thứ tự: từ dưới lên trên, từ phải qua trái</t>
+          <t>1. Con trỏ di chuyển ngược lại theo thứ tự: từ dưới lên trên, từ phải qua trái</t>
         </is>
       </c>
       <c r="F18" s="683" t="n"/>
@@ -3764,7 +3765,7 @@
       </c>
       <c r="E19" s="685" t="inlineStr">
         <is>
-          <t>Màn hình thu nhỏ, phóng to tương ứng và không bị vỡ giao diện</t>
+          <t>3. Màn hình thu nhỏ, phóng to tương ứng và không bị vỡ giao diện</t>
         </is>
       </c>
       <c r="F19" s="683" t="n"/>
@@ -3798,7 +3799,7 @@
       </c>
       <c r="E20" s="685" t="inlineStr">
         <is>
-          <t>Menu con Quản lý gói cước được highlight (đang chọn), nhóm menu Quản lý gói cước ở trạng thái mở rộng</t>
+          <t>1. Menu con Quản lý gói cước được highlight (đang chọn), nhóm menu Quản lý gói cước ở trạng thái mở rộng</t>
         </is>
       </c>
       <c r="F20" s="683" t="n"/>
@@ -3859,7 +3860,7 @@
       </c>
       <c r="E22" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị tiêu đề: Quản lý gói cước</t>
+          <t>1. Hiển thị tiêu đề: Quản lý gói cước</t>
         </is>
       </c>
       <c r="F22" s="683" t="n"/>
@@ -3901,7 +3902,7 @@
       </c>
       <c r="E23" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị button text "Thêm gói cước", trạng thái enable</t>
+          <t>1. Hiển thị button text "Thêm gói cước", trạng thái enable</t>
         </is>
       </c>
       <c r="F23" s="683" t="n"/>
@@ -3939,7 +3940,8 @@
       </c>
       <c r="E24" s="685" t="inlineStr">
         <is>
-          <t>- Điều hướng đến màn Tạo gói cước mới
+          <t>1. 
+- Điều hướng đến màn Tạo gói cước mới
 - Trường Loại gói cước để trống, cho phép chọn loại gói</t>
         </is>
       </c>
@@ -3982,7 +3984,7 @@
       </c>
       <c r="E25" s="685" t="inlineStr">
         <is>
-          <t>Mặc định trống, hiển thị placeholder: "Tìm kiếm theo tên, mã gói cước"</t>
+          <t>1. Mặc định trống, hiển thị placeholder: "Tìm kiếm theo tên, mã gói cước"</t>
         </is>
       </c>
       <c r="F25" s="683" t="n"/>
@@ -4020,7 +4022,7 @@
       </c>
       <c r="E26" s="685" t="inlineStr">
         <is>
-          <t>Cho phép nhập, hiển thị đúng dữ liệu vừa nhập</t>
+          <t>1. Cho phép nhập, hiển thị đúng dữ liệu vừa nhập</t>
         </is>
       </c>
       <c r="F26" s="683" t="inlineStr">
@@ -4066,7 +4068,7 @@
       </c>
       <c r="E27" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị button viền, icon bảng tính màu xanh lá + text "Xuất file excel", trạng thái enable</t>
+          <t>1. Hiển thị button viền, icon bảng tính màu xanh lá + text "Xuất file excel", trạng thái enable</t>
         </is>
       </c>
       <c r="F27" s="683" t="n"/>
@@ -4104,7 +4106,7 @@
       </c>
       <c r="E28" s="685" t="inlineStr">
         <is>
-          <t>Thực hiện chức năng xuất file excel theo UC Xuất file excel</t>
+          <t>1. Thực hiện chức năng xuất file excel theo UC Xuất file excel</t>
         </is>
       </c>
       <c r="F28" s="683" t="n"/>
@@ -4146,7 +4148,7 @@
       </c>
       <c r="E29" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị button viền, icon bánh răng + text "Cài đặt bảng", trạng thái enable</t>
+          <t>1. Hiển thị button viền, icon bánh răng + text "Cài đặt bảng", trạng thái enable</t>
         </is>
       </c>
       <c r="F29" s="683" t="n"/>
@@ -4184,7 +4186,7 @@
       </c>
       <c r="E30" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị popup cấu hình ẩn/hiện các cột dữ liệu của bảng danh sách gói cước</t>
+          <t>1. Hiển thị popup cấu hình ẩn/hiện các cột dữ liệu của bảng danh sách gói cước</t>
         </is>
       </c>
       <c r="F30" s="683" t="n"/>
@@ -4226,7 +4228,7 @@
       </c>
       <c r="E31" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị icon phễu lọc, trạng thái enable</t>
+          <t>1. Hiển thị icon phễu lọc, trạng thái enable</t>
         </is>
       </c>
       <c r="F31" s="683" t="n"/>
@@ -4264,7 +4266,7 @@
       </c>
       <c r="E32" s="685" t="inlineStr">
         <is>
-          <t>Mở tab bộ lọc</t>
+          <t>1. Mở tab bộ lọc</t>
         </is>
       </c>
       <c r="F32" s="683" t="n"/>
@@ -4327,7 +4329,7 @@
       </c>
       <c r="E34" s="685" t="inlineStr">
         <is>
-          <t>Không hiển thị bảng dữ liệu. Hiển thị text "Danh sách trống"</t>
+          <t>2. Không hiển thị bảng dữ liệu. Hiển thị text "Danh sách trống"</t>
         </is>
       </c>
       <c r="F34" s="683" t="n"/>
@@ -4371,7 +4373,7 @@
       </c>
       <c r="E35" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị danh sách dạng nhóm: dòng cha là Loại gói cước, bên dưới là bảng con gói cước trực thuộc</t>
+          <t>2. Hiển thị danh sách dạng nhóm: dòng cha là Loại gói cước, bên dưới là bảng con gói cước trực thuộc</t>
         </is>
       </c>
       <c r="F35" s="683" t="n"/>
@@ -4414,7 +4416,8 @@
       </c>
       <c r="E36" s="685" t="inlineStr">
         <is>
-          <t>- Tất cả dòng cha ở trạng thái thu gọn, chỉ thấy dòng cha
+          <t>2. 
+- Tất cả dòng cha ở trạng thái thu gọn, chỉ thấy dòng cha
 - Icon mũi tên hướng xuống ⌄</t>
         </is>
       </c>
@@ -4458,7 +4461,8 @@
       </c>
       <c r="E37" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị bảng con danh sách gói cước thuộc loại gói đó
+          <t>1. 
+- Hiển thị bảng con danh sách gói cước thuộc loại gói đó
 - Icon đổi thành mũi tên hướng lên ⌃</t>
         </is>
       </c>
@@ -4498,7 +4502,8 @@
       </c>
       <c r="E38" s="685" t="inlineStr">
         <is>
-          <t>- Ẩn bảng con danh sách gói cước
+          <t>1. 
+- Ẩn bảng con danh sách gói cước
 - Icon đổi thành mũi tên hướng xuống ⌄</t>
         </is>
       </c>
@@ -4538,7 +4543,7 @@
       </c>
       <c r="E39" s="685" t="inlineStr">
         <is>
-          <t>Cả 2 dòng cha cùng mở rộng, mở dòng B không làm thu gọn dòng A</t>
+          <t>2. Cả 2 dòng cha cùng mở rộng, mở dòng B không làm thu gọn dòng A</t>
         </is>
       </c>
       <c r="F39" s="683" t="n"/>
@@ -4577,7 +4582,8 @@
       </c>
       <c r="E40" s="685" t="inlineStr">
         <is>
-          <t>- Bảng con không có dòng gói cước nào
+          <t>1. 
+- Bảng con không có dòng gói cước nào
 - Vẫn hiển thị link "+ Thêm gói cước"</t>
         </is>
       </c>
@@ -4617,7 +4623,7 @@
       </c>
       <c r="E41" s="685" t="inlineStr">
         <is>
-          <t>Tất cả dòng cha trở về trạng thái thu gọn mặc định</t>
+          <t>1. Tất cả dòng cha trở về trạng thái thu gọn mặc định</t>
         </is>
       </c>
       <c r="F41" s="683" t="n"/>
@@ -4659,7 +4665,7 @@
       </c>
       <c r="E42" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "Tên loại gói: &lt;Tên loại gói cước&gt;" đúng dữ liệu đã tạo tại Quản lý loại gói cước</t>
+          <t>1. Hiển thị "Tên loại gói: &lt;Tên loại gói cước&gt;" đúng dữ liệu đã tạo tại Quản lý loại gói cước</t>
         </is>
       </c>
       <c r="F42" s="683" t="inlineStr">
@@ -4702,7 +4708,8 @@
       </c>
       <c r="E43" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị loại gói A
+          <t>1. 
+- Hiển thị loại gói A
 - Không hiển thị loại gói B</t>
         </is>
       </c>
@@ -4743,7 +4750,7 @@
       </c>
       <c r="E44" s="685" t="inlineStr">
         <is>
-          <t>Không còn hiển thị dòng cha loại gói A</t>
+          <t>2. Không còn hiển thị dòng cha loại gói A</t>
         </is>
       </c>
       <c r="F44" s="683" t="n"/>
@@ -4782,7 +4789,7 @@
       </c>
       <c r="E45" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị dòng cha loại gói vừa tạo, badge số lượng = 0, đúng vị trí sắp xếp mặc định</t>
+          <t>2. Hiển thị dòng cha loại gói vừa tạo, badge số lượng = 0, đúng vị trí sắp xếp mặc định</t>
         </is>
       </c>
       <c r="F45" s="683" t="n"/>
@@ -4821,7 +4828,7 @@
       </c>
       <c r="E46" s="685" t="inlineStr">
         <is>
-          <t>Thứ tự mặc định sắp xếp theo tên loại dịch vụ từ A-Z</t>
+          <t>1. Thứ tự mặc định sắp xếp theo tên loại dịch vụ từ A-Z</t>
         </is>
       </c>
       <c r="F46" s="683" t="n"/>
@@ -4864,7 +4871,7 @@
       </c>
       <c r="E47" s="685" t="inlineStr">
         <is>
-          <t>Badge hiển thị số 3</t>
+          <t>1. Badge hiển thị số 3</t>
         </is>
       </c>
       <c r="F47" s="683" t="n"/>
@@ -4903,7 +4910,7 @@
       </c>
       <c r="E48" s="685" t="inlineStr">
         <is>
-          <t>Badge hiển thị số 3</t>
+          <t>1. Badge hiển thị số 3</t>
         </is>
       </c>
       <c r="F48" s="683" t="n"/>
@@ -4943,7 +4950,7 @@
       </c>
       <c r="E49" s="685" t="inlineStr">
         <is>
-          <t>Badge loại gói A hiển thị X+1</t>
+          <t>2. Badge loại gói A hiển thị X+1</t>
         </is>
       </c>
       <c r="F49" s="683" t="n"/>
@@ -4983,7 +4990,7 @@
       </c>
       <c r="E50" s="685" t="inlineStr">
         <is>
-          <t>Badge loại gói A hiển thị X-1</t>
+          <t>2. Badge loại gói A hiển thị X-1</t>
         </is>
       </c>
       <c r="F50" s="683" t="n"/>
@@ -5022,7 +5029,7 @@
       </c>
       <c r="E51" s="685" t="inlineStr">
         <is>
-          <t>Badge hiển thị số 0</t>
+          <t>1. Badge hiển thị số 0</t>
         </is>
       </c>
       <c r="F51" s="683" t="n"/>
@@ -5064,7 +5071,7 @@
       </c>
       <c r="E52" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "Loại dịch vụ: &lt;giá trị&gt;" đúng loại dịch vụ của loại gói cước (OA, Meeting, Thiết bị...)</t>
+          <t>1. Hiển thị "Loại dịch vụ: &lt;giá trị&gt;" đúng loại dịch vụ của loại gói cước (OA, Meeting, Thiết bị...)</t>
         </is>
       </c>
       <c r="F52" s="683" t="n"/>
@@ -5107,7 +5114,7 @@
       </c>
       <c r="E53" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "Loại hình OA áp dụng: &lt;tên loại hình&gt;" sắp xếp tên A-Z, cách nhau dấu ";"</t>
+          <t>1. Hiển thị "Loại hình OA áp dụng: &lt;tên loại hình&gt;" sắp xếp tên A-Z, cách nhau dấu ";"</t>
         </is>
       </c>
       <c r="F53" s="683" t="inlineStr">
@@ -5150,7 +5157,7 @@
       </c>
       <c r="E54" s="685" t="inlineStr">
         <is>
-          <t>Không hiển thị thông tin Loại hình OA áp dụng</t>
+          <t>1. Không hiển thị thông tin Loại hình OA áp dụng</t>
         </is>
       </c>
       <c r="F54" s="683" t="n"/>
@@ -5189,7 +5196,7 @@
       </c>
       <c r="E55" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 20 ký tự đầu, phần còn lại thay bằng "…"</t>
+          <t>1. Hiển thị 20 ký tự đầu, phần còn lại thay bằng "…"</t>
         </is>
       </c>
       <c r="F55" s="683" t="inlineStr">
@@ -5232,7 +5239,7 @@
       </c>
       <c r="E56" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đầy đủ 20 ký tự, không có "…"</t>
+          <t>1. Hiển thị đầy đủ 20 ký tự, không có "…"</t>
         </is>
       </c>
       <c r="F56" s="683" t="inlineStr">
@@ -5279,7 +5286,7 @@
       </c>
       <c r="E57" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "Danh mục OA áp dụng: &lt;tên danh mục&gt;" sắp xếp tên A-Z, cách nhau dấu ";"</t>
+          <t>1. Hiển thị "Danh mục OA áp dụng: &lt;tên danh mục&gt;" sắp xếp tên A-Z, cách nhau dấu ";"</t>
         </is>
       </c>
       <c r="F57" s="683" t="n"/>
@@ -5318,7 +5325,7 @@
       </c>
       <c r="E58" s="685" t="inlineStr">
         <is>
-          <t>Không hiển thị thông tin Danh mục OA áp dụng</t>
+          <t>1. Không hiển thị thông tin Danh mục OA áp dụng</t>
         </is>
       </c>
       <c r="F58" s="683" t="n"/>
@@ -5357,7 +5364,7 @@
       </c>
       <c r="E59" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 20 ký tự đầu, phần còn lại thay bằng "…"</t>
+          <t>1. Hiển thị 20 ký tự đầu, phần còn lại thay bằng "…"</t>
         </is>
       </c>
       <c r="F59" s="683" t="inlineStr">
@@ -5403,7 +5410,7 @@
       </c>
       <c r="E60" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "Phạm vi áp dụng: &lt;Tài khoản OA / Tài khoản Tammi&gt;" theo design</t>
+          <t>1. Hiển thị "Phạm vi áp dụng: &lt;Tài khoản OA / Tài khoản Tammi&gt;" theo design</t>
         </is>
       </c>
       <c r="F60" s="683" t="n"/>
@@ -5465,7 +5472,7 @@
       </c>
       <c r="E62" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị các cột: Mã gói, Chu kỳ, Giá gốc (VNĐ), Kênh bán, Loại hình, Trạng thái, Thời gian cập nhật, Người cập nhật, Thao tác</t>
+          <t>1. Hiển thị các cột: Mã gói, Chu kỳ, Giá gốc (VNĐ), Kênh bán, Loại hình, Trạng thái, Thời gian cập nhật, Người cập nhật, Thao tác</t>
         </is>
       </c>
       <c r="F62" s="683" t="n"/>
@@ -5504,7 +5511,7 @@
       </c>
       <c r="E63" s="685" t="inlineStr">
         <is>
-          <t>Cột Thao tác luôn hiển thị cố định bên phải, các cột khác cuộn bình thường, không vỡ layout</t>
+          <t>1. Cột Thao tác luôn hiển thị cố định bên phải, các cột khác cuộn bình thường, không vỡ layout</t>
         </is>
       </c>
       <c r="F63" s="683" t="n"/>
@@ -5547,7 +5554,8 @@
       </c>
       <c r="E64" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị 4 gói ở trạng thái Nháp, Đã phát hành, Đang kinh doanh, Ngừng kinh doanh
+          <t>1. 
+- Hiển thị 4 gói ở trạng thái Nháp, Đã phát hành, Đang kinh doanh, Ngừng kinh doanh
 - Không hiển thị gói Đã xoá</t>
         </is>
       </c>
@@ -5587,7 +5595,7 @@
       </c>
       <c r="E65" s="685" t="inlineStr">
         <is>
-          <t>Gói cước hiển thị đúng dưới loại gói cước sở hữu, không lẫn sang loại gói khác</t>
+          <t>2. Gói cước hiển thị đúng dưới loại gói cước sở hữu, không lẫn sang loại gói khác</t>
         </is>
       </c>
       <c r="F65" s="683" t="n"/>
@@ -5626,7 +5634,7 @@
       </c>
       <c r="E66" s="685" t="inlineStr">
         <is>
-          <t>Sắp xếp theo chu kỳ quy đổi ra ngày từ bé đến lớn: 7 ngày, 2 tuần, 12 tháng, 1 năm</t>
+          <t>1. Sắp xếp theo chu kỳ quy đổi ra ngày từ bé đến lớn: 7 ngày, 2 tuần, 12 tháng, 1 năm</t>
         </is>
       </c>
       <c r="F66" s="683" t="inlineStr">
@@ -5672,7 +5680,7 @@
       </c>
       <c r="E67" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị mã gói dạng text in hoa, đúng mã đã tạo</t>
+          <t>1. Hiển thị mã gói dạng text in hoa, đúng mã đã tạo</t>
         </is>
       </c>
       <c r="F67" s="683" t="inlineStr">
@@ -5719,7 +5727,7 @@
       </c>
       <c r="E68" s="685" t="inlineStr">
         <is>
-          <t>Danh sách gói con của loại gói đó sắp xếp theo Mã gói A-Z</t>
+          <t>2. Danh sách gói con của loại gói đó sắp xếp theo Mã gói A-Z</t>
         </is>
       </c>
       <c r="F68" s="683" t="n"/>
@@ -5757,7 +5765,7 @@
       </c>
       <c r="E69" s="685" t="inlineStr">
         <is>
-          <t>Danh sách gói con sắp xếp theo Mã gói Z-A</t>
+          <t>1. Danh sách gói con sắp xếp theo Mã gói Z-A</t>
         </is>
       </c>
       <c r="F69" s="683" t="n"/>
@@ -6076,7 +6084,8 @@
       </c>
       <c r="E77" s="685" t="inlineStr">
         <is>
-          <t>- Chỉ danh sách gói con của loại gói A thay đổi thứ tự
+          <t>1. 
+- Chỉ danh sách gói con của loại gói A thay đổi thứ tự
 - Bảng con loại gói B và thứ tự dòng cha không đổi</t>
         </is>
       </c>
@@ -6119,7 +6128,7 @@
       </c>
       <c r="E78" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị [Số] [Đơn vị], VD: 7 tháng, 12 tháng, 24 tháng</t>
+          <t>1. Hiển thị [Số] [Đơn vị], VD: 7 tháng, 12 tháng, 24 tháng</t>
         </is>
       </c>
       <c r="F78" s="683" t="n"/>
@@ -6158,7 +6167,7 @@
       </c>
       <c r="E79" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đúng đơn vị đã lưu khi tạo: "30 ngày", "2 tuần", "12 tháng", "1 năm" (không tự quy đổi)</t>
+          <t>1. Hiển thị đúng đơn vị đã lưu khi tạo: "30 ngày", "2 tuần", "12 tháng", "1 năm" (không tự quy đổi)</t>
         </is>
       </c>
       <c r="F79" s="683" t="n"/>
@@ -6200,7 +6209,7 @@
       </c>
       <c r="E80" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị số tiền có dấu chấm phân cách hàng nghìn, VD: 1.200.000</t>
+          <t>1. Hiển thị số tiền có dấu chấm phân cách hàng nghìn, VD: 1.200.000</t>
         </is>
       </c>
       <c r="F80" s="683" t="inlineStr">
@@ -6243,7 +6252,7 @@
       </c>
       <c r="E81" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đúng 9.999.999.999.999, không vỡ layout, không hiển thị dạng số mũ</t>
+          <t>1. Hiển thị đúng 9.999.999.999.999, không vỡ layout, không hiển thị dạng số mũ</t>
         </is>
       </c>
       <c r="F81" s="683" t="inlineStr">
@@ -6290,7 +6299,7 @@
       </c>
       <c r="E82" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị: Web OA</t>
+          <t>1. Hiển thị: Web OA</t>
         </is>
       </c>
       <c r="F82" s="683" t="n"/>
@@ -6329,7 +6338,7 @@
       </c>
       <c r="E83" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ 2 kênh, text dài cắt "..." như design ("Mini app gói cước...")</t>
+          <t>1. Hiển thị đủ 2 kênh, text dài cắt "..." như design ("Mini app gói cước...")</t>
         </is>
       </c>
       <c r="F83" s="683" t="n"/>
@@ -6372,7 +6381,7 @@
       </c>
       <c r="E84" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đúng: Chính / Add-on</t>
+          <t>1. Hiển thị đúng: Chính / Add-on</t>
         </is>
       </c>
       <c r="F84" s="683" t="n"/>
@@ -6415,7 +6424,7 @@
       </c>
       <c r="E85" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị status pill "Nháp" màu xám theo design</t>
+          <t>1. Hiển thị status pill "Nháp" màu xám theo design</t>
         </is>
       </c>
       <c r="F85" s="683" t="n"/>
@@ -6454,7 +6463,7 @@
       </c>
       <c r="E86" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị status pill "Đã phát hành" màu vàng theo design</t>
+          <t>1. Hiển thị status pill "Đã phát hành" màu vàng theo design</t>
         </is>
       </c>
       <c r="F86" s="683" t="n"/>
@@ -6493,7 +6502,7 @@
       </c>
       <c r="E87" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị status pill "Đang kinh doanh" màu xanh theo design</t>
+          <t>1. Hiển thị status pill "Đang kinh doanh" màu xanh theo design</t>
         </is>
       </c>
       <c r="F87" s="683" t="n"/>
@@ -6532,7 +6541,7 @@
       </c>
       <c r="E88" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị status pill "Ngừng kinh doanh" màu đỏ theo design</t>
+          <t>1. Hiển thị status pill "Ngừng kinh doanh" màu đỏ theo design</t>
         </is>
       </c>
       <c r="F88" s="683" t="n"/>
@@ -6572,7 +6581,7 @@
       </c>
       <c r="E89" s="685" t="inlineStr">
         <is>
-          <t>Cột Trạng thái của gói hiển thị "Đang kinh doanh"</t>
+          <t>2. Cột Trạng thái của gói hiển thị "Đang kinh doanh"</t>
         </is>
       </c>
       <c r="F89" s="683" t="n"/>
@@ -6614,7 +6623,7 @@
       </c>
       <c r="E90" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị thời điểm cập nhật gần nhất định dạng DD/MM/YYYY HH:mm:ss</t>
+          <t>1. Hiển thị thời điểm cập nhật gần nhất định dạng DD/MM/YYYY HH:mm:ss</t>
         </is>
       </c>
       <c r="F90" s="683" t="inlineStr">
@@ -6657,7 +6666,7 @@
       </c>
       <c r="E91" s="685" t="inlineStr">
         <is>
-          <t>Thời gian cập nhật = thời điểm lưu chỉnh sửa, Người cập nhật = họ tên Admin B</t>
+          <t>2. Thời gian cập nhật = thời điểm lưu chỉnh sửa, Người cập nhật = họ tên Admin B</t>
         </is>
       </c>
       <c r="F91" s="683" t="n"/>
@@ -6699,7 +6708,7 @@
       </c>
       <c r="E92" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị họ và tên tài khoản Admin thực hiện cập nhật gần nhất</t>
+          <t>1. Hiển thị họ và tên tài khoản Admin thực hiện cập nhật gần nhất</t>
         </is>
       </c>
       <c r="F92" s="683" t="inlineStr">
@@ -6745,7 +6754,7 @@
       </c>
       <c r="E93" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 3 icon: (i) Xem chi tiết, ✏ Chỉnh sửa, 🗑 Xoá</t>
+          <t>1. Hiển thị 3 icon: (i) Xem chi tiết, ✏ Chỉnh sửa, 🗑 Xoá</t>
         </is>
       </c>
       <c r="F93" s="683" t="n"/>
@@ -6783,7 +6792,7 @@
       </c>
       <c r="E94" s="685" t="inlineStr">
         <is>
-          <t>Điều hướng đến trang Xem chi tiết đúng gói cước đã chọn</t>
+          <t>1. Điều hướng đến trang Xem chi tiết đúng gói cước đã chọn</t>
         </is>
       </c>
       <c r="F94" s="683" t="n"/>
@@ -6821,7 +6830,7 @@
       </c>
       <c r="E95" s="685" t="inlineStr">
         <is>
-          <t>Điều hướng đến trang Chỉnh sửa đúng gói cước đã chọn</t>
+          <t>1. Điều hướng đến trang Chỉnh sửa đúng gói cước đã chọn</t>
         </is>
       </c>
       <c r="F95" s="683" t="n"/>
@@ -6859,7 +6868,7 @@
       </c>
       <c r="E96" s="685" t="inlineStr">
         <is>
-          <t>Thực hiện luồng Xoá gói cước theo UC xoá gói cước (hiển thị popup xác nhận)</t>
+          <t>1. Thực hiện luồng Xoá gói cước theo UC xoá gói cước (hiển thị popup xác nhận)</t>
         </is>
       </c>
       <c r="F96" s="683" t="n"/>
@@ -6898,7 +6907,7 @@
       </c>
       <c r="E97" s="685" t="inlineStr">
         <is>
-          <t>Theo bảng trạng thái: gói Đang kinh doanh tuyệt đối không được xoá; Nháp được xoá; Đã phát hành/Ngừng kinh doanh chỉ xoá khi chưa phát sinh giao dịch</t>
+          <t>1. Theo bảng trạng thái: gói Đang kinh doanh tuyệt đối không được xoá; Nháp được xoá; Đã phát hành/Ngừng kinh doanh chỉ xoá khi chưa phát sinh giao dịch</t>
         </is>
       </c>
       <c r="F97" s="683" t="n"/>
@@ -6941,7 +6950,7 @@
       </c>
       <c r="E98" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị text màu đỏ "+ Thêm gói cước"</t>
+          <t>1. Hiển thị text màu đỏ "+ Thêm gói cước"</t>
         </is>
       </c>
       <c r="F98" s="683" t="n"/>
@@ -6980,7 +6989,8 @@
       </c>
       <c r="E99" s="685" t="inlineStr">
         <is>
-          <t>- Điều hướng đến form Tạo gói cước mới
+          <t>1. 
+- Điều hướng đến form Tạo gói cước mới
 - Trường Loại gói cước tự gán sẵn "Plus OA Business"
 - Danh sách tính năng hiển thị theo loại gói đó</t>
         </is>
@@ -7043,7 +7053,7 @@
       </c>
       <c r="E101" s="685" t="inlineStr">
         <is>
-          <t>Mặc định hiển thị "10 dòng", mỗi trang tối đa 10 loại gói cước (dòng cha)</t>
+          <t>1. Mặc định hiển thị "10 dòng", mỗi trang tối đa 10 loại gói cước (dòng cha)</t>
         </is>
       </c>
       <c r="F101" s="683" t="n"/>
@@ -7081,7 +7091,7 @@
       </c>
       <c r="E102" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị các giá trị: 10, 15, 20, 25</t>
+          <t>1. Hiển thị các giá trị: 10, 15, 20, 25</t>
         </is>
       </c>
       <c r="F102" s="683" t="n"/>
@@ -7101,7 +7111,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="32" customHeight="1" s="668">
+    <row r="103" ht="48" customHeight="1" s="668">
       <c r="A103" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D103),"00")</f>
         <v/>
@@ -7120,7 +7130,8 @@
       </c>
       <c r="E103" s="685" t="inlineStr">
         <is>
-          <t>- Tải lại dữ liệu, tự động quay về trang 1
+          <t>1. 
+- Tải lại dữ liệu, tự động quay về trang 1
 - Hiển thị tối đa 20 loại gói cước/trang</t>
         </is>
       </c>
@@ -7161,7 +7172,7 @@
       </c>
       <c r="E104" s="685" t="inlineStr">
         <is>
-          <t>Trang 1 hiển thị 10 loại gói cước kèm toàn bộ gói con; loại gói thứ 11 ở trang 2</t>
+          <t>2. Trang 1 hiển thị 10 loại gói cước kèm toàn bộ gói con; loại gói thứ 11 ở trang 2</t>
         </is>
       </c>
       <c r="F104" s="683" t="n"/>
@@ -7204,7 +7215,7 @@
       </c>
       <c r="E105" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị: "Hiển thị 1–10 trong tổng số 112 kết quả"</t>
+          <t>1. Hiển thị: "Hiển thị 1–10 trong tổng số 112 kết quả"</t>
         </is>
       </c>
       <c r="F105" s="683" t="n"/>
@@ -7243,7 +7254,7 @@
       </c>
       <c r="E106" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị: "Hiển thị 111–112 trong tổng số 112 kết quả"</t>
+          <t>1. Hiển thị: "Hiển thị 111–112 trong tổng số 112 kết quả"</t>
         </is>
       </c>
       <c r="F106" s="683" t="n"/>
@@ -7286,7 +7297,7 @@
       </c>
       <c r="E107" s="685" t="inlineStr">
         <is>
-          <t>Nút ← bị vô hiệu hoá</t>
+          <t>2. Nút ← bị vô hiệu hoá</t>
         </is>
       </c>
       <c r="F107" s="683" t="n"/>
@@ -7325,7 +7336,7 @@
       </c>
       <c r="E108" s="685" t="inlineStr">
         <is>
-          <t>Nút → bị vô hiệu hoá</t>
+          <t>2. Nút → bị vô hiệu hoá</t>
         </is>
       </c>
       <c r="F108" s="683" t="n"/>
@@ -7345,7 +7356,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="32" customHeight="1" s="668">
+    <row r="109" ht="48" customHeight="1" s="668">
       <c r="A109" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D109),"00")</f>
         <v/>
@@ -7363,7 +7374,8 @@
       </c>
       <c r="E109" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị dữ liệu trang 2, nối tiếp trang 1
+          <t>1. 
+- Hiển thị dữ liệu trang 2, nối tiếp trang 1
 - Số trang 2 active nền/chữ đỏ</t>
         </is>
       </c>
@@ -7443,7 +7455,7 @@
       </c>
       <c r="E111" s="685" t="inlineStr">
         <is>
-          <t>Chỉ có 1 trang, nút ← và → đều bị vô hiệu hoá</t>
+          <t>1. Chỉ có 1 trang, nút ← và → đều bị vô hiệu hoá</t>
         </is>
       </c>
       <c r="F111" s="683" t="n"/>
@@ -7482,7 +7494,7 @@
       </c>
       <c r="E112" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 1, 2, 3, ..., 15 theo design</t>
+          <t>1. Hiển thị 1, 2, 3, ..., 15 theo design</t>
         </is>
       </c>
       <c r="F112" s="683" t="n"/>
@@ -7521,7 +7533,7 @@
       <c r="L113" s="683" t="n"/>
       <c r="M113" s="683" t="n"/>
     </row>
-    <row r="114" ht="32" customHeight="1" s="668">
+    <row r="114" ht="48" customHeight="1" s="668">
       <c r="A114" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D114),"00")</f>
         <v/>
@@ -7544,7 +7556,7 @@
       </c>
       <c r="E114" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị toast "Thất bại. Vui lòng kiểm tra lại kết nối." và cho phép người dùng thử lại</t>
+          <t>2. Hiển thị toast "Thất bại. Vui lòng kiểm tra lại kết nối." và cho phép người dùng thử lại</t>
         </is>
       </c>
       <c r="F114" s="683" t="n"/>
@@ -7584,7 +7596,7 @@
       </c>
       <c r="E115" s="685" t="inlineStr">
         <is>
-          <t>Danh sách tải thành công, hiển thị đúng dữ liệu</t>
+          <t>2. Danh sách tải thành công, hiển thị đúng dữ liệu</t>
         </is>
       </c>
       <c r="F115" s="683" t="n"/>
@@ -7627,7 +7639,7 @@
       </c>
       <c r="E116" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị toast "Hệ thống bận. Vui lòng thử lại sau." kèm mã lỗi tương ứng, cho phép thử lại</t>
+          <t>1. Hiển thị toast "Hệ thống bận. Vui lòng thử lại sau." kèm mã lỗi tương ứng, cho phép thử lại</t>
         </is>
       </c>
       <c r="F116" s="683" t="n"/>
@@ -7671,7 +7683,7 @@
       </c>
       <c r="E117" s="685" t="inlineStr">
         <is>
-          <t>Không hiển thị menu Quản lý gói cước; truy cập URL trực tiếp bị chặn</t>
+          <t>2. Không hiển thị menu Quản lý gói cước; truy cập URL trực tiếp bị chặn</t>
         </is>
       </c>
       <c r="F117" s="683" t="n"/>
@@ -7714,7 +7726,7 @@
       </c>
       <c r="E118" s="685" t="inlineStr">
         <is>
-          <t>Dữ liệu hiển thị khớp CSDL; xem danh sách không làm thay đổi dữ liệu</t>
+          <t>2. Dữ liệu hiển thị khớp CSDL; xem danh sách không làm thay đổi dữ liệu</t>
         </is>
       </c>
       <c r="F118" s="683" t="n"/>
@@ -7758,7 +7770,7 @@
       </c>
       <c r="E119" s="685" t="inlineStr">
         <is>
-          <t>API phản hồi &lt; 500ms</t>
+          <t>2. API phản hồi &lt; 500ms</t>
         </is>
       </c>
       <c r="F119" s="683" t="n"/>
@@ -7839,7 +7851,7 @@
       <c r="L122" s="683" t="n"/>
       <c r="M122" s="683" t="n"/>
     </row>
-    <row r="123" ht="112" customHeight="1" s="668">
+    <row r="123" ht="128" customHeight="1" s="668">
       <c r="A123" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D123),"00")</f>
         <v/>
@@ -7862,7 +7874,7 @@
       </c>
       <c r="E123" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị màn Tạo gói cước mới đúng design gồm:
+          <t>2. Hiển thị màn Tạo gói cước mới đúng design gồm:
 + Icon Back, tiêu đề "Tạo gói cước mới", button Lưu
 + Khối Thông tin cơ bản: Mã gói cước, Tag, Mô tả, Chu kỳ, Đơn vị, Giá gốc, Đơn vị tính
 + Khối Thuộc tính: Loại hình gói, Kênh bán, Bật/tắt trạng thái và các trường phụ thuộc
@@ -7899,15 +7911,16 @@
       </c>
       <c r="D124" s="685" t="inlineStr">
         <is>
-          <t>Kiểm tra về bố cục, font chữ, chính tả, màu chữ</t>
+          <t>1. Kiểm tra về bố cục, font chữ, chính tả, màu chữ</t>
         </is>
       </c>
       <c r="E124" s="685" t="inlineStr">
         <is>
-          <t>1. Các label, có độ dài, rộng và khoảng cách bằng nhau, không xô lệch
-2. Các label sử dụng cùng 1 loại font, cỡ chữ, căn lề
-3. Kiểm tra tất cả lỗi về chính tả, cấu trúc câu, ngữ pháp trên màn hình
-4. Form được bố trí hợp lý và dễ sử dụng</t>
+          <t>1. 
+- Các label, có độ dài, rộng và khoảng cách bằng nhau, không xô lệch
+- Các label sử dụng cùng 1 loại font, cỡ chữ, căn lề
+- Kiểm tra tất cả lỗi về chính tả, cấu trúc câu, ngữ pháp trên màn hình
+- Form được bố trí hợp lý và dễ sử dụng</t>
         </is>
       </c>
       <c r="F124" s="683" t="n"/>
@@ -7942,7 +7955,7 @@
       </c>
       <c r="E125" s="685" t="inlineStr">
         <is>
-          <t>Con trỏ di chuyển lần lượt theo thứ tự: Từ trái qua phải, từ trên xuống dưới</t>
+          <t>2. Con trỏ di chuyển lần lượt theo thứ tự: Từ trái qua phải, từ trên xuống dưới</t>
         </is>
       </c>
       <c r="F125" s="683" t="n"/>
@@ -7977,7 +7990,7 @@
       </c>
       <c r="E126" s="685" t="inlineStr">
         <is>
-          <t>Con trỏ di chuyển ngược lại theo thứ tự: từ dưới lên trên, từ phải qua trái</t>
+          <t>2. Con trỏ di chuyển ngược lại theo thứ tự: từ dưới lên trên, từ phải qua trái</t>
         </is>
       </c>
       <c r="F126" s="683" t="n"/>
@@ -8011,7 +8024,7 @@
       </c>
       <c r="E127" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị màn hình phóng to, thu nhỏ không bị xô lệch, vỡ form</t>
+          <t>1. Hiển thị màn hình phóng to, thu nhỏ không bị xô lệch, vỡ form</t>
         </is>
       </c>
       <c r="F127" s="683" t="n"/>
@@ -8045,7 +8058,7 @@
       </c>
       <c r="E128" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị tiêu đề text là "Tạo gói cước mới"</t>
+          <t>1. Hiển thị tiêu đề text là "Tạo gói cước mới"</t>
         </is>
       </c>
       <c r="F128" s="683" t="n"/>
@@ -8083,7 +8096,7 @@
       </c>
       <c r="E129" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị dấu * đỏ tại: Mã gói cước, Chu kỳ, Đơn vị, Giá gốc, Đơn vị tính, Loại hình gói, Kênh bán, Bật/tắt trạng thái, Loại gói cước, Tham số</t>
+          <t>1. Hiển thị dấu * đỏ tại: Mã gói cước, Chu kỳ, Đơn vị, Giá gốc, Đơn vị tính, Loại hình gói, Kênh bán, Bật/tắt trạng thái, Loại gói cước, Tham số</t>
         </is>
       </c>
       <c r="F129" s="683" t="n"/>
@@ -8103,7 +8116,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="80" customHeight="1" s="668">
+    <row r="130" ht="96" customHeight="1" s="668">
       <c r="A130" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D130),"00")</f>
         <v/>
@@ -8121,7 +8134,8 @@
       </c>
       <c r="E130" s="685" t="inlineStr">
         <is>
-          <t>- Mã gói, Mô tả, Chu kỳ, Giá gốc, Tag, Kênh bán: rỗng
+          <t>1. 
+- Mã gói, Mô tả, Chu kỳ, Giá gốc, Tag, Kênh bán: rỗng
 - Đơn vị: Ngày; Đơn vị tính: VNĐ
 - Loại hình gói: Gói chính
 - Bật/tắt trạng thái: Thủ công; Trạng thái kinh doanh: Đang kinh doanh
@@ -8163,7 +8177,7 @@
       </c>
       <c r="E131" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị button "Lưu" góc phải trên, trạng thái enable</t>
+          <t>1. Hiển thị button "Lưu" góc phải trên, trạng thái enable</t>
         </is>
       </c>
       <c r="F131" s="683" t="n"/>
@@ -8224,7 +8238,7 @@
       </c>
       <c r="E133" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị trường Mã gói cước ban đầu mặc định trống</t>
+          <t>1. Hiển thị trường Mã gói cước ban đầu mặc định trống</t>
         </is>
       </c>
       <c r="F133" s="683" t="n"/>
@@ -8264,7 +8278,7 @@
       </c>
       <c r="E134" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin", không lưu gói cước</t>
+          <t>3. Hiển thị lỗi inline: "Vui lòng nhập thông tin", không lưu gói cước</t>
         </is>
       </c>
       <c r="F134" s="683" t="n"/>
@@ -8303,7 +8317,7 @@
       </c>
       <c r="E135" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
+          <t>2. Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
         </is>
       </c>
       <c r="F135" s="683" t="inlineStr">
@@ -8345,7 +8359,7 @@
       </c>
       <c r="E136" s="685" t="inlineStr">
         <is>
-          <t>Trường tự động hiển thị "OAPLUS30"</t>
+          <t>1. Trường tự động hiển thị "OAPLUS30"</t>
         </is>
       </c>
       <c r="F136" s="683" t="inlineStr">
@@ -8387,7 +8401,7 @@
       </c>
       <c r="E137" s="685" t="inlineStr">
         <is>
-          <t>Trường tự động hiển thị dạng viết hoa không dấu: "GOI CUOC UU DAI"</t>
+          <t>1. Trường tự động hiển thị dạng viết hoa không dấu: "GOI CUOC UU DAI"</t>
         </is>
       </c>
       <c r="F137" s="683" t="inlineStr">
@@ -8430,7 +8444,7 @@
       </c>
       <c r="E138" s="685" t="inlineStr">
         <is>
-          <t>Hệ thống xử lý theo rule ký tự của mã gói</t>
+          <t>2. Hệ thống xử lý theo rule ký tự của mã gói</t>
         </is>
       </c>
       <c r="F138" s="683" t="inlineStr">
@@ -8473,7 +8487,7 @@
       </c>
       <c r="E139" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ 49 ký tự vừa nhập, không báo lỗi</t>
+          <t>2. Hiển thị đủ 49 ký tự vừa nhập, không báo lỗi</t>
         </is>
       </c>
       <c r="F139" s="683" t="inlineStr">
@@ -8516,7 +8530,7 @@
       </c>
       <c r="E140" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ 50 ký tự vừa nhập, không báo lỗi</t>
+          <t>2. Hiển thị đủ 50 ký tự vừa nhập, không báo lỗi</t>
         </is>
       </c>
       <c r="F140" s="683" t="inlineStr">
@@ -8559,7 +8573,7 @@
       </c>
       <c r="E141" s="685" t="inlineStr">
         <is>
-          <t>Chặn nhập ký tự thứ 51, chỉ cho phép 50 ký tự</t>
+          <t>2. Chặn nhập ký tự thứ 51, chỉ cho phép 50 ký tự</t>
         </is>
       </c>
       <c r="F141" s="683" t="inlineStr">
@@ -8602,7 +8616,7 @@
       </c>
       <c r="E142" s="685" t="inlineStr">
         <is>
-          <t>Chỉ giữ 50 ký tự đầu</t>
+          <t>1. Chỉ giữ 50 ký tự đầu</t>
         </is>
       </c>
       <c r="F142" s="683" t="inlineStr">
@@ -8647,7 +8661,7 @@
       </c>
       <c r="E143" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Mã gói đã được sử dụng", không lưu gói cước</t>
+          <t>3. Hiển thị lỗi inline: "Mã gói đã được sử dụng", không lưu gói cước</t>
         </is>
       </c>
       <c r="F143" s="683" t="inlineStr">
@@ -8691,7 +8705,7 @@
       </c>
       <c r="E144" s="685" t="inlineStr">
         <is>
-          <t>Cả 3 trường hợp đều hiển thị lỗi inline: "Mã gói đã được sử dụng"</t>
+          <t>2. Cả 3 trường hợp đều hiển thị lỗi inline: "Mã gói đã được sử dụng"</t>
         </is>
       </c>
       <c r="F144" s="683" t="n"/>
@@ -8732,7 +8746,7 @@
       </c>
       <c r="E145" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu, tạo gói cước thành công</t>
+          <t>3. Cho phép lưu, tạo gói cước thành công</t>
         </is>
       </c>
       <c r="F145" s="683" t="inlineStr">
@@ -8776,7 +8790,7 @@
       </c>
       <c r="E146" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Mã gói đã được sử dụng" (mã duy nhất toàn hệ thống)</t>
+          <t>2. Hiển thị lỗi inline: "Mã gói đã được sử dụng" (mã duy nhất toàn hệ thống)</t>
         </is>
       </c>
       <c r="F146" s="683" t="n"/>
@@ -8816,7 +8830,7 @@
       </c>
       <c r="E147" s="685" t="inlineStr">
         <is>
-          <t>Mã tự chuyển thành "OAPLUS30" và báo lỗi "Mã gói đã được sử dụng"</t>
+          <t>2. Mã tự chuyển thành "OAPLUS30" và báo lỗi "Mã gói đã được sử dụng"</t>
         </is>
       </c>
       <c r="F147" s="683" t="inlineStr">
@@ -8859,7 +8873,7 @@
       </c>
       <c r="E148" s="685" t="inlineStr">
         <is>
-          <t>Paste dữ liệu thành công, áp dụng rule viết hoa/không dấu</t>
+          <t>2. Paste dữ liệu thành công, áp dụng rule viết hoa/không dấu</t>
         </is>
       </c>
       <c r="F148" s="683" t="n"/>
@@ -8897,7 +8911,7 @@
       </c>
       <c r="E149" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị trường Mô tả dạng textarea, mặc định trống</t>
+          <t>1. Hiển thị trường Mô tả dạng textarea, mặc định trống</t>
         </is>
       </c>
       <c r="F149" s="683" t="n"/>
@@ -8937,7 +8951,7 @@
       </c>
       <c r="E150" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu thành công (trường không bắt buộc)</t>
+          <t>3. Cho phép lưu thành công (trường không bắt buộc)</t>
         </is>
       </c>
       <c r="F150" s="683" t="n"/>
@@ -8975,7 +8989,7 @@
       </c>
       <c r="E151" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ dữ liệu vừa nhập</t>
+          <t>1. Hiển thị đủ dữ liệu vừa nhập</t>
         </is>
       </c>
       <c r="F151" s="683" t="inlineStr">
@@ -9017,7 +9031,7 @@
       </c>
       <c r="E152" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ dữ liệu vừa nhập</t>
+          <t>1. Hiển thị đủ dữ liệu vừa nhập</t>
         </is>
       </c>
       <c r="F152" s="683" t="inlineStr">
@@ -9059,7 +9073,7 @@
       </c>
       <c r="E153" s="685" t="inlineStr">
         <is>
-          <t>Chặn nhập ký tự thứ 501, chỉ cho phép 500 ký tự</t>
+          <t>1. Chặn nhập ký tự thứ 501, chỉ cho phép 500 ký tự</t>
         </is>
       </c>
       <c r="F153" s="683" t="inlineStr">
@@ -9102,7 +9116,7 @@
       </c>
       <c r="E154" s="685" t="inlineStr">
         <is>
-          <t>Cho phép nhập và lưu đúng dữ liệu</t>
+          <t>2. Cho phép nhập và lưu đúng dữ liệu</t>
         </is>
       </c>
       <c r="F154" s="683" t="inlineStr">
@@ -9145,7 +9159,7 @@
       </c>
       <c r="E155" s="685" t="inlineStr">
         <is>
-          <t>Mô tả hiển thị đúng định dạng gạch đầu dòng</t>
+          <t>2. Mô tả hiển thị đúng định dạng gạch đầu dòng</t>
         </is>
       </c>
       <c r="F155" s="683" t="inlineStr">
@@ -9188,7 +9202,7 @@
       </c>
       <c r="E156" s="685" t="inlineStr">
         <is>
-          <t>Không thực thi script, hiển thị dạng text</t>
+          <t>2. Không thực thi script, hiển thị dạng text</t>
         </is>
       </c>
       <c r="F156" s="683" t="inlineStr">
@@ -9235,7 +9249,7 @@
       </c>
       <c r="E157" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
+          <t>2. Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
         </is>
       </c>
       <c r="F157" s="683" t="n"/>
@@ -9274,7 +9288,7 @@
       </c>
       <c r="E158" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu, chu kỳ phải là số nguyên dương &gt; 0</t>
+          <t>2. Không cho phép lưu, chu kỳ phải là số nguyên dương &gt; 0</t>
         </is>
       </c>
       <c r="F158" s="683" t="inlineStr">
@@ -9318,7 +9332,7 @@
       </c>
       <c r="E159" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu thành công</t>
+          <t>3. Cho phép lưu thành công</t>
         </is>
       </c>
       <c r="F159" s="683" t="inlineStr">
@@ -9360,7 +9374,7 @@
       </c>
       <c r="E160" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập dấu "-"</t>
+          <t>1. Chặn không cho nhập dấu "-"</t>
         </is>
       </c>
       <c r="F160" s="683" t="inlineStr">
@@ -9402,7 +9416,7 @@
       </c>
       <c r="E161" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập (chỉ cho số nguyên)</t>
+          <t>1. Chặn không cho nhập (chỉ cho số nguyên)</t>
         </is>
       </c>
       <c r="F161" s="683" t="inlineStr">
@@ -9444,7 +9458,7 @@
       </c>
       <c r="E162" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập</t>
+          <t>1. Chặn không cho nhập</t>
         </is>
       </c>
       <c r="F162" s="683" t="inlineStr">
@@ -9487,7 +9501,7 @@
       </c>
       <c r="E163" s="685" t="inlineStr">
         <is>
-          <t>Chặn/báo lỗi khi vượt giới hạn INT</t>
+          <t>2. Chặn/báo lỗi khi vượt giới hạn INT</t>
         </is>
       </c>
       <c r="F163" s="683" t="inlineStr">
@@ -9531,7 +9545,7 @@
       </c>
       <c r="E164" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói", không lưu</t>
+          <t>2. Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói", không lưu</t>
         </is>
       </c>
       <c r="F164" s="683" t="inlineStr">
@@ -9575,7 +9589,7 @@
       </c>
       <c r="E165" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói" (1 tháng = 30 ngày)</t>
+          <t>2. Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói" (1 tháng = 30 ngày)</t>
         </is>
       </c>
       <c r="F165" s="683" t="inlineStr">
@@ -9619,7 +9633,7 @@
       </c>
       <c r="E166" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói" (2 tuần = 14 ngày)</t>
+          <t>2. Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói" (2 tuần = 14 ngày)</t>
         </is>
       </c>
       <c r="F166" s="683" t="inlineStr">
@@ -9663,7 +9677,7 @@
       </c>
       <c r="E167" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói" (1 năm = 360 ngày = 12 tháng)</t>
+          <t>2. Hiển thị lỗi: "Đã có gói cùng chu kì thuộc cùng loại gói" (1 năm = 360 ngày = 12 tháng)</t>
         </is>
       </c>
       <c r="F167" s="683" t="inlineStr">
@@ -9707,7 +9721,7 @@
       </c>
       <c r="E168" s="685" t="inlineStr">
         <is>
-          <t>Cả 2 gói đều lưu thành công</t>
+          <t>2. Cả 2 gói đều lưu thành công</t>
         </is>
       </c>
       <c r="F168" s="683" t="inlineStr">
@@ -9751,7 +9765,7 @@
       </c>
       <c r="E169" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu thành công</t>
+          <t>2. Cho phép lưu thành công</t>
         </is>
       </c>
       <c r="F169" s="683" t="n"/>
@@ -9791,7 +9805,7 @@
       </c>
       <c r="E170" s="685" t="inlineStr">
         <is>
-          <t>Tất cả trường hợp đều báo lỗi "Đã có gói cùng chu kì thuộc cùng loại gói"</t>
+          <t>2. Tất cả trường hợp đều báo lỗi "Đã có gói cùng chu kì thuộc cùng loại gói"</t>
         </is>
       </c>
       <c r="F170" s="683" t="n"/>
@@ -9831,7 +9845,7 @@
       </c>
       <c r="E171" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu thành công</t>
+          <t>2. Cho phép lưu thành công</t>
         </is>
       </c>
       <c r="F171" s="683" t="n"/>
@@ -9873,7 +9887,7 @@
       </c>
       <c r="E172" s="685" t="inlineStr">
         <is>
-          <t>Mặc định chọn "Ngày"</t>
+          <t>1. Mặc định chọn "Ngày"</t>
         </is>
       </c>
       <c r="F172" s="683" t="n"/>
@@ -9911,7 +9925,7 @@
       </c>
       <c r="E173" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 4 giá trị: Ngày, Tuần, Tháng, Năm</t>
+          <t>1. Hiển thị 4 giá trị: Ngày, Tuần, Tháng, Năm</t>
         </is>
       </c>
       <c r="F173" s="683" t="n"/>
@@ -9949,7 +9963,7 @@
       </c>
       <c r="E174" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "Tháng", đóng dropdown; chỉ chọn được 1 giá trị</t>
+          <t>1. Hiển thị "Tháng", đóng dropdown; chỉ chọn được 1 giá trị</t>
         </is>
       </c>
       <c r="F174" s="683" t="n"/>
@@ -9992,7 +10006,7 @@
       </c>
       <c r="E175" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
+          <t>2. Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
         </is>
       </c>
       <c r="F175" s="683" t="n"/>
@@ -10030,7 +10044,7 @@
       </c>
       <c r="E176" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "1.119.000"</t>
+          <t>1. Hiển thị "1.119.000"</t>
         </is>
       </c>
       <c r="F176" s="683" t="inlineStr">
@@ -10073,7 +10087,7 @@
       </c>
       <c r="E177" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu, giá gốc phải &gt; 0</t>
+          <t>2. Không cho phép lưu, giá gốc phải &gt; 0</t>
         </is>
       </c>
       <c r="F177" s="683" t="inlineStr">
@@ -10117,7 +10131,7 @@
       </c>
       <c r="E178" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu thành công</t>
+          <t>3. Cho phép lưu thành công</t>
         </is>
       </c>
       <c r="F178" s="683" t="inlineStr">
@@ -10159,7 +10173,7 @@
       </c>
       <c r="E179" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập dấu "-"</t>
+          <t>1. Chặn không cho nhập dấu "-"</t>
         </is>
       </c>
       <c r="F179" s="683" t="inlineStr">
@@ -10201,7 +10215,7 @@
       </c>
       <c r="E180" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập phần thập phân (số tiền nguyên)</t>
+          <t>1. Chặn không cho nhập phần thập phân (số tiền nguyên)</t>
         </is>
       </c>
       <c r="F180" s="683" t="inlineStr">
@@ -10243,7 +10257,7 @@
       </c>
       <c r="E181" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập</t>
+          <t>1. Chặn không cho nhập</t>
         </is>
       </c>
       <c r="F181" s="683" t="inlineStr">
@@ -10285,7 +10299,7 @@
       </c>
       <c r="E182" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "9.999.999.999.999", cho phép lưu</t>
+          <t>1. Hiển thị "9.999.999.999.999", cho phép lưu</t>
         </is>
       </c>
       <c r="F182" s="683" t="inlineStr">
@@ -10327,7 +10341,7 @@
       </c>
       <c r="E183" s="685" t="inlineStr">
         <is>
-          <t>Chặn nhập chữ số thứ 14</t>
+          <t>1. Chặn nhập chữ số thứ 14</t>
         </is>
       </c>
       <c r="F183" s="683" t="inlineStr">
@@ -10374,7 +10388,7 @@
       </c>
       <c r="E184" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị "VNĐ" dạng read-only (nền xám), không sửa được</t>
+          <t>2. Hiển thị "VNĐ" dạng read-only (nền xám), không sửa được</t>
         </is>
       </c>
       <c r="F184" s="683" t="n"/>
@@ -10416,7 +10430,7 @@
       </c>
       <c r="E185" s="685" t="inlineStr">
         <is>
-          <t>Mặc định "Gói chính"</t>
+          <t>1. Mặc định "Gói chính"</t>
         </is>
       </c>
       <c r="F185" s="683" t="n"/>
@@ -10454,7 +10468,7 @@
       </c>
       <c r="E186" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 2 lựa chọn: Gói chính, Gói add-on</t>
+          <t>1. Hiển thị 2 lựa chọn: Gói chính, Gói add-on</t>
         </is>
       </c>
       <c r="F186" s="683" t="n"/>
@@ -10494,7 +10508,7 @@
       </c>
       <c r="E187" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, danh sách hiển thị Loại hình = Add-on</t>
+          <t>3. Lưu thành công, danh sách hiển thị Loại hình = Add-on</t>
         </is>
       </c>
       <c r="F187" s="683" t="n"/>
@@ -10538,7 +10552,7 @@
       </c>
       <c r="E188" s="685" t="inlineStr">
         <is>
-          <t>Cho phép lưu thành công (trường không bắt buộc)</t>
+          <t>3. Cho phép lưu thành công (trường không bắt buộc)</t>
         </is>
       </c>
       <c r="F188" s="683" t="n"/>
@@ -10576,7 +10590,7 @@
       </c>
       <c r="E189" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ 50 ký tự</t>
+          <t>1. Hiển thị đủ 50 ký tự</t>
         </is>
       </c>
       <c r="F189" s="683" t="inlineStr">
@@ -10618,7 +10632,7 @@
       </c>
       <c r="E190" s="685" t="inlineStr">
         <is>
-          <t>Chặn nhập ký tự thứ 51</t>
+          <t>1. Chặn nhập ký tự thứ 51</t>
         </is>
       </c>
       <c r="F190" s="683" t="inlineStr">
@@ -10661,7 +10675,7 @@
       </c>
       <c r="E191" s="685" t="inlineStr">
         <is>
-          <t>Cho phép nhập và lưu đúng dữ liệu</t>
+          <t>2. Cho phép nhập và lưu đúng dữ liệu</t>
         </is>
       </c>
       <c r="F191" s="683" t="inlineStr">
@@ -10707,7 +10721,7 @@
       </c>
       <c r="E192" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị 2 lựa chọn: Miniapp gói cước Tammi, Web OA</t>
+          <t>1. Hiển thị 2 lựa chọn: Miniapp gói cước Tammi, Web OA</t>
         </is>
       </c>
       <c r="F192" s="683" t="n"/>
@@ -10746,7 +10760,7 @@
       </c>
       <c r="E193" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi bắt buộc, không lưu gói cước</t>
+          <t>2. Hiển thị lỗi bắt buộc, không lưu gói cước</t>
         </is>
       </c>
       <c r="F193" s="683" t="n"/>
@@ -10786,7 +10800,7 @@
       </c>
       <c r="E194" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, distribution_channels = ["WEB_OA"]</t>
+          <t>3. Lưu thành công, distribution_channels = ["WEB_OA"]</t>
         </is>
       </c>
       <c r="F194" s="683" t="n"/>
@@ -10825,7 +10839,7 @@
       </c>
       <c r="E195" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, distribution_channels = ["WEB_OA", "MINIAPP_TAMMI"]</t>
+          <t>2. Lưu thành công, distribution_channels = ["WEB_OA", "MINIAPP_TAMMI"]</t>
         </is>
       </c>
       <c r="F195" s="683" t="n"/>
@@ -10864,7 +10878,7 @@
       </c>
       <c r="E196" s="685" t="inlineStr">
         <is>
-          <t>Trường Kênh bán trở về rỗng</t>
+          <t>2. Trường Kênh bán trở về rỗng</t>
         </is>
       </c>
       <c r="F196" s="683" t="n"/>
@@ -10907,7 +10921,7 @@
       </c>
       <c r="E197" s="685" t="inlineStr">
         <is>
-          <t>Chỉ 1 lựa chọn được tick tại 1 thời điểm; chọn Tự động thì Thủ công tự bỏ tick</t>
+          <t>2. Chỉ 1 lựa chọn được tick tại 1 thời điểm; chọn Tự động thì Thủ công tự bỏ tick</t>
         </is>
       </c>
       <c r="F197" s="683" t="n"/>
@@ -10946,7 +10960,8 @@
       </c>
       <c r="E198" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị trường Trạng thái kinh doanh (Đang kinh doanh / Ngừng kinh doanh)
+          <t>2. 
+- Hiển thị trường Trạng thái kinh doanh (Đang kinh doanh / Ngừng kinh doanh)
 - Ẩn/không bắt buộc Thời gian bắt đầu, Thời gian kết thúc</t>
         </is>
       </c>
@@ -10986,7 +11001,8 @@
       </c>
       <c r="E199" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị Thời gian bắt đầu *, Thời gian kết thúc *
+          <t>2. 
+- Hiển thị Thời gian bắt đầu *, Thời gian kết thúc *
 - Ẩn trường Trạng thái kinh doanh</t>
         </is>
       </c>
@@ -11027,7 +11043,7 @@
       </c>
       <c r="E200" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, không validate thời gian; start_time/end_time không lưu</t>
+          <t>3. Lưu thành công, không validate thời gian; start_time/end_time không lưu</t>
         </is>
       </c>
       <c r="F200" s="683" t="n"/>
@@ -11113,7 +11129,7 @@
       </c>
       <c r="E202" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, gói trạng thái Nháp, Sale_status = PENDING</t>
+          <t>3. Lưu thành công, gói trạng thái Nháp, Sale_status = PENDING</t>
         </is>
       </c>
       <c r="F202" s="683" t="n"/>
@@ -11156,7 +11172,7 @@
       </c>
       <c r="E203" s="685" t="inlineStr">
         <is>
-          <t>Mặc định ngày hiện tại</t>
+          <t>1. Mặc định ngày hiện tại</t>
         </is>
       </c>
       <c r="F203" s="683" t="n"/>
@@ -11195,7 +11211,7 @@
       </c>
       <c r="E204" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị định dạng DD/MM/YYYY HH:mm:ss</t>
+          <t>1. Hiển thị định dạng DD/MM/YYYY HH:mm:ss</t>
         </is>
       </c>
       <c r="F204" s="683" t="inlineStr">
@@ -11239,7 +11255,7 @@
       </c>
       <c r="E205" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
+          <t>2. Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
         </is>
       </c>
       <c r="F205" s="683" t="n"/>
@@ -11279,7 +11295,7 @@
       </c>
       <c r="E206" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu / không cho chọn thời điểm quá khứ</t>
+          <t>2. Không cho phép lưu / không cho chọn thời điểm quá khứ</t>
         </is>
       </c>
       <c r="F206" s="683" t="inlineStr">
@@ -11323,7 +11339,7 @@
       </c>
       <c r="E207" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu (yêu cầu &gt; hiện tại)</t>
+          <t>2. Không cho phép lưu (yêu cầu &gt; hiện tại)</t>
         </is>
       </c>
       <c r="F207" s="683" t="inlineStr">
@@ -11367,7 +11383,7 @@
       </c>
       <c r="E208" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công</t>
+          <t>2. Lưu thành công</t>
         </is>
       </c>
       <c r="F208" s="683" t="inlineStr">
@@ -11414,7 +11430,7 @@
       </c>
       <c r="E209" s="685" t="inlineStr">
         <is>
-          <t>Mặc định rỗng</t>
+          <t>1. Mặc định rỗng</t>
         </is>
       </c>
       <c r="F209" s="683" t="n"/>
@@ -11454,7 +11470,7 @@
       </c>
       <c r="E210" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
+          <t>2. Hiển thị lỗi inline: "Vui lòng nhập thông tin"</t>
         </is>
       </c>
       <c r="F210" s="683" t="n"/>
@@ -11494,7 +11510,7 @@
       </c>
       <c r="E211" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu, báo lỗi thời gian kết thúc phải &gt; thời gian bắt đầu</t>
+          <t>2. Không cho phép lưu, báo lỗi thời gian kết thúc phải &gt; thời gian bắt đầu</t>
         </is>
       </c>
       <c r="F211" s="683" t="n"/>
@@ -11534,7 +11550,7 @@
       </c>
       <c r="E212" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu</t>
+          <t>2. Không cho phép lưu</t>
         </is>
       </c>
       <c r="F212" s="683" t="n"/>
@@ -11574,7 +11590,7 @@
       </c>
       <c r="E213" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công</t>
+          <t>2. Lưu thành công</t>
         </is>
       </c>
       <c r="F213" s="683" t="n"/>
@@ -11613,7 +11629,7 @@
       </c>
       <c r="E214" s="685" t="inlineStr">
         <is>
-          <t>Không nhận giá trị không hợp lệ, báo lỗi định dạng</t>
+          <t>1. Không nhận giá trị không hợp lệ, báo lỗi định dạng</t>
         </is>
       </c>
       <c r="F214" s="683" t="inlineStr">
@@ -11661,7 +11677,7 @@
       </c>
       <c r="E215" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, max_purchase_quantity = null (không giới hạn)</t>
+          <t>3. Lưu thành công, max_purchase_quantity = null (không giới hạn)</t>
         </is>
       </c>
       <c r="F215" s="683" t="n"/>
@@ -11700,7 +11716,7 @@
       </c>
       <c r="E216" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, hiểu là không giới hạn</t>
+          <t>2. Lưu thành công, hiểu là không giới hạn</t>
         </is>
       </c>
       <c r="F216" s="683" t="inlineStr">
@@ -11743,7 +11759,7 @@
       </c>
       <c r="E217" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, mỗi user chỉ đăng ký được 1 lần</t>
+          <t>2. Lưu thành công, mỗi user chỉ đăng ký được 1 lần</t>
         </is>
       </c>
       <c r="F217" s="683" t="inlineStr">
@@ -11785,7 +11801,7 @@
       </c>
       <c r="E218" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập</t>
+          <t>1. Chặn không cho nhập</t>
         </is>
       </c>
       <c r="F218" s="683" t="inlineStr">
@@ -11832,7 +11848,7 @@
       </c>
       <c r="E219" s="685" t="inlineStr">
         <is>
-          <t>Trường Loại gói cước hiển thị "Plus OA Business"</t>
+          <t>2. Trường Loại gói cước hiển thị "Plus OA Business"</t>
         </is>
       </c>
       <c r="F219" s="683" t="n"/>
@@ -11852,7 +11868,7 @@
         </is>
       </c>
     </row>
-    <row r="220" ht="32" customHeight="1" s="668">
+    <row r="220" ht="48" customHeight="1" s="668">
       <c r="A220" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D220),"00")</f>
         <v/>
@@ -11871,7 +11887,8 @@
       </c>
       <c r="E220" s="685" t="inlineStr">
         <is>
-          <t>- Trường Loại gói cước rỗng
+          <t>2. 
+- Trường Loại gói cước rỗng
 - Khối Danh sách tính năng chưa hiển thị tính năng</t>
         </is>
       </c>
@@ -11911,7 +11928,7 @@
       </c>
       <c r="E221" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị danh sách loại gói cước trạng thái Đang hoạt động, không có loại gói Đã xoá</t>
+          <t>1. Hiển thị danh sách loại gói cước trạng thái Đang hoạt động, không có loại gói Đã xoá</t>
         </is>
       </c>
       <c r="F221" s="683" t="n"/>
@@ -11951,7 +11968,7 @@
       </c>
       <c r="E222" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi bắt buộc, không lưu</t>
+          <t>2. Hiển thị lỗi bắt buộc, không lưu</t>
         </is>
       </c>
       <c r="F222" s="683" t="n"/>
@@ -11990,7 +12007,7 @@
       </c>
       <c r="E223" s="685" t="inlineStr">
         <is>
-          <t>Danh sách tính năng thay đổi theo loại gói B, tham số đã nhập của loại gói A bị xoá</t>
+          <t>2. Danh sách tính năng thay đổi theo loại gói B, tham số đã nhập của loại gói A bị xoá</t>
         </is>
       </c>
       <c r="F223" s="683" t="n"/>
@@ -12029,7 +12046,7 @@
       </c>
       <c r="E224" s="685" t="inlineStr">
         <is>
-          <t>Trường hiển thị read-only (nền xám) theo design, không đổi được</t>
+          <t>1. Trường hiển thị read-only (nền xám) theo design, không đổi được</t>
         </is>
       </c>
       <c r="F224" s="683" t="n"/>
@@ -12071,7 +12088,7 @@
       </c>
       <c r="E225" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị các cột: STT, Mã tính năng, Tên tính năng, Nhóm tính năng, Tên tham số</t>
+          <t>1. Hiển thị các cột: STT, Mã tính năng, Tên tính năng, Nhóm tính năng, Tên tham số</t>
         </is>
       </c>
       <c r="F225" s="683" t="n"/>
@@ -12109,7 +12126,7 @@
       </c>
       <c r="E226" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ tất cả tính năng thuộc loại gói, sắp xếp tăng dần theo STT hiển thị</t>
+          <t>1. Hiển thị đủ tất cả tính năng thuộc loại gói, sắp xếp tăng dần theo STT hiển thị</t>
         </is>
       </c>
       <c r="F226" s="683" t="n"/>
@@ -12147,7 +12164,7 @@
       </c>
       <c r="E227" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép chỉnh sửa</t>
+          <t>1. Không cho phép chỉnh sửa</t>
         </is>
       </c>
       <c r="F227" s="683" t="n"/>
@@ -12185,7 +12202,7 @@
       </c>
       <c r="E228" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị full mô tả, không cắt</t>
+          <t>1. Hiển thị full mô tả, không cắt</t>
         </is>
       </c>
       <c r="F228" s="683" t="n"/>
@@ -12223,7 +12240,7 @@
       </c>
       <c r="E229" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị đủ các ô tham số, không vỡ layout</t>
+          <t>1. Hiển thị đủ các ô tham số, không vỡ layout</t>
         </is>
       </c>
       <c r="F229" s="683" t="n"/>
@@ -12265,7 +12282,7 @@
       </c>
       <c r="E230" s="685" t="inlineStr">
         <is>
-          <t>Label = Tên tham số + Đơn vị tính, VD "Số cộng đồng (ĐVT: Cộng đồng) *"</t>
+          <t>1. Label = Tên tham số + Đơn vị tính, VD "Số cộng đồng (ĐVT: Cộng đồng) *"</t>
         </is>
       </c>
       <c r="F230" s="683" t="n"/>
@@ -12304,7 +12321,7 @@
       </c>
       <c r="E231" s="685" t="inlineStr">
         <is>
-          <t>Tham số sắp xếp theo tên A-Z</t>
+          <t>1. Tham số sắp xếp theo tên A-Z</t>
         </is>
       </c>
       <c r="F231" s="683" t="n"/>
@@ -12343,7 +12360,7 @@
       </c>
       <c r="E232" s="685" t="inlineStr">
         <is>
-          <t>Không hiển thị ô nhập tham số</t>
+          <t>1. Không hiển thị ô nhập tham số</t>
         </is>
       </c>
       <c r="F232" s="683" t="n"/>
@@ -12382,7 +12399,7 @@
       </c>
       <c r="E233" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline: "Vui lòng nhập thông tin" tại ô trống, không lưu</t>
+          <t>2. Hiển thị lỗi inline: "Vui lòng nhập thông tin" tại ô trống, không lưu</t>
         </is>
       </c>
       <c r="F233" s="683" t="n"/>
@@ -12421,7 +12438,7 @@
       </c>
       <c r="E234" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, quota_value lưu đúng giá trị</t>
+          <t>2. Lưu thành công, quota_value lưu đúng giá trị</t>
         </is>
       </c>
       <c r="F234" s="683" t="inlineStr">
@@ -12464,7 +12481,7 @@
       </c>
       <c r="E235" s="685" t="inlineStr">
         <is>
-          <t>Lưu thành công, quota_value = CÓ/KHÔNG</t>
+          <t>2. Lưu thành công, quota_value = CÓ/KHÔNG</t>
         </is>
       </c>
       <c r="F235" s="683" t="n"/>
@@ -12502,7 +12519,7 @@
       </c>
       <c r="E236" s="685" t="inlineStr">
         <is>
-          <t>Chặn không cho nhập / báo lỗi theo rule tham số</t>
+          <t>1. Chặn không cho nhập / báo lỗi theo rule tham số</t>
         </is>
       </c>
       <c r="F236" s="683" t="inlineStr">
@@ -12569,7 +12586,8 @@
       </c>
       <c r="E238" s="685" t="inlineStr">
         <is>
-          <t>- Hiển thị popup: icon thành công, tiêu đề "Thêm mới gói cước thành công", nội dung "Bạn đã thêm mới gói cước [Mã gói cước vừa tạo]", button Đóng, icon X
+          <t>3. 
+- Hiển thị popup: icon thành công, tiêu đề "Thêm mới gói cước thành công", nội dung "Bạn đã thêm mới gói cước [Mã gói cước vừa tạo]", button Đóng, icon X
 - Gói cước được lưu vào CSDL</t>
         </is>
       </c>
@@ -12613,7 +12631,7 @@
       </c>
       <c r="E239" s="685" t="inlineStr">
         <is>
-          <t>Gói cước có trạng thái Nháp (DRAFT)</t>
+          <t>2. Gói cước có trạng thái Nháp (DRAFT)</t>
         </is>
       </c>
       <c r="F239" s="683" t="n"/>
@@ -12652,7 +12670,7 @@
       </c>
       <c r="E240" s="685" t="inlineStr">
         <is>
-          <t>Lưu đúng: plan_type_id, plan_code, description, billing_cycle_value/unit, original_price, currency = VND, plan_role, marketing_tag, distribution_channels, activation_mode, start_time/end_time hoặc Sale_status, is_renew = FALSE, status = DRAFT, created_by/at, updated_by/at</t>
+          <t>2. Lưu đúng: plan_type_id, plan_code, description, billing_cycle_value/unit, original_price, currency = VND, plan_role, marketing_tag, distribution_channels, activation_mode, start_time/end_time hoặc Sale_status, is_renew = FALSE, status = DRAFT, created_by/at, updated_by/at</t>
         </is>
       </c>
       <c r="F240" s="683" t="n"/>
@@ -12691,7 +12709,7 @@
       </c>
       <c r="E241" s="685" t="inlineStr">
         <is>
-          <t>Mỗi tham số sinh 1 bản ghi: plan_id, feature_id, parameter_id, quota_value đúng giá trị đã nhập</t>
+          <t>2. Mỗi tham số sinh 1 bản ghi: plan_id, feature_id, parameter_id, quota_value đúng giá trị đã nhập</t>
         </is>
       </c>
       <c r="F241" s="683" t="n"/>
@@ -12730,7 +12748,7 @@
       </c>
       <c r="E242" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị lỗi inline tại tất cả trường bắt buộc cùng lúc, focus về trường lỗi đầu tiên</t>
+          <t>2. Hiển thị lỗi inline tại tất cả trường bắt buộc cùng lúc, focus về trường lỗi đầu tiên</t>
         </is>
       </c>
       <c r="F242" s="683" t="n"/>
@@ -12769,7 +12787,7 @@
       </c>
       <c r="E243" s="685" t="inlineStr">
         <is>
-          <t>Chỉ tạo 1 gói cước, không tạo bản ghi trùng</t>
+          <t>2. Chỉ tạo 1 gói cước, không tạo bản ghi trùng</t>
         </is>
       </c>
       <c r="F243" s="683" t="n"/>
@@ -12789,7 +12807,7 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="48" customHeight="1" s="668">
+    <row r="244" ht="64" customHeight="1" s="668">
       <c r="A244" s="684">
         <f>$C$4&amp;"-"&amp;TEXT(COUNTA($D$12:D244),"00")</f>
         <v/>
@@ -12808,7 +12826,8 @@
       </c>
       <c r="E244" s="685" t="inlineStr">
         <is>
-          <t>- Gói mới hiển thị trong bảng con đúng loại gói, đúng vị trí theo chu kỳ
+          <t>2. 
+- Gói mới hiển thị trong bảng con đúng loại gói, đúng vị trí theo chu kỳ
 - Badge số lượng tăng 1
 - Người cập nhật = Admin tạo</t>
         </is>
@@ -12849,7 +12868,7 @@
       </c>
       <c r="E245" s="685" t="inlineStr">
         <is>
-          <t>Ghi log: người tạo, thời gian, IP, giá trị mới</t>
+          <t>2. Ghi log: người tạo, thời gian, IP, giá trị mới</t>
         </is>
       </c>
       <c r="F245" s="683" t="n"/>
@@ -12892,7 +12911,7 @@
       </c>
       <c r="E246" s="685" t="inlineStr">
         <is>
-          <t>Đóng popup, chuyển hướng về màn hình Danh sách gói cước</t>
+          <t>2. Đóng popup, chuyển hướng về màn hình Danh sách gói cước</t>
         </is>
       </c>
       <c r="F246" s="683" t="n"/>
@@ -12931,7 +12950,7 @@
       </c>
       <c r="E247" s="685" t="inlineStr">
         <is>
-          <t>Tương tự button Đóng</t>
+          <t>2. Tương tự button Đóng</t>
         </is>
       </c>
       <c r="F247" s="683" t="n"/>
@@ -12974,7 +12993,7 @@
       </c>
       <c r="E248" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị popup xác nhận: tiêu đề "Huỷ tạo mới gói cước", nội dung "Các thông tin đã nhập sẽ không được lưu. Bạn có chắc chắn muốn thoát?", button Quay lại, Xác nhận</t>
+          <t>2. Hiển thị popup xác nhận: tiêu đề "Huỷ tạo mới gói cước", nội dung "Các thông tin đã nhập sẽ không được lưu. Bạn có chắc chắn muốn thoát?", button Quay lại, Xác nhận</t>
         </is>
       </c>
       <c r="F248" s="683" t="n"/>
@@ -13013,7 +13032,7 @@
       </c>
       <c r="E249" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị popup xác nhận huỷ (AF01 áp dụng tại bất kỳ bước nào)</t>
+          <t>2. Hiển thị popup xác nhận huỷ (AF01 áp dụng tại bất kỳ bước nào)</t>
         </is>
       </c>
       <c r="F249" s="683" t="n"/>
@@ -13053,7 +13072,7 @@
       </c>
       <c r="E250" s="685" t="inlineStr">
         <is>
-          <t>Đóng popup, quay về Danh sách gói cước, không lưu dữ liệu, không phát sinh bản ghi mới</t>
+          <t>3. Đóng popup, quay về Danh sách gói cước, không lưu dữ liệu, không phát sinh bản ghi mới</t>
         </is>
       </c>
       <c r="F250" s="683" t="n"/>
@@ -13093,7 +13112,7 @@
       </c>
       <c r="E251" s="685" t="inlineStr">
         <is>
-          <t>Đóng popup, ở lại form, dữ liệu đã nhập được giữ nguyên</t>
+          <t>3. Đóng popup, ở lại form, dữ liệu đã nhập được giữ nguyên</t>
         </is>
       </c>
       <c r="F251" s="683" t="n"/>
@@ -13132,7 +13151,7 @@
       </c>
       <c r="E252" s="685" t="inlineStr">
         <is>
-          <t>Xử lý tương tự icon Back (hiển thị popup xác nhận huỷ)</t>
+          <t>2. Xử lý tương tự icon Back (hiển thị popup xác nhận huỷ)</t>
         </is>
       </c>
       <c r="F252" s="683" t="n"/>
@@ -13176,7 +13195,7 @@
       </c>
       <c r="E253" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị toast "Thất bại. Vui lòng kiểm tra lại kết nối.", giữ dữ liệu trên form, cho phép thử lại</t>
+          <t>3. Hiển thị toast "Thất bại. Vui lòng kiểm tra lại kết nối.", giữ dữ liệu trên form, cho phép thử lại</t>
         </is>
       </c>
       <c r="F253" s="683" t="n"/>
@@ -13215,7 +13234,7 @@
       </c>
       <c r="E254" s="685" t="inlineStr">
         <is>
-          <t>Hiển thị toast "Hệ thống bận. Vui lòng thử lại sau." kèm mã lỗi, cho phép thử lại</t>
+          <t>1. Hiển thị toast "Hệ thống bận. Vui lòng thử lại sau." kèm mã lỗi, cho phép thử lại</t>
         </is>
       </c>
       <c r="F254" s="683" t="n"/>
@@ -13249,14 +13268,15 @@
       <c r="D255" s="685" t="inlineStr">
         <is>
           <t>ĐK: Admin A và B cùng mở form
-1. Cả 2 nhập mã "OAPLUS90"
-2. A click Lưu, sau đó B click Lưu</t>
+1. Cả 2 nhập mã "OAPLUS90" và đủ các trường hợp lệ
+2. Admin A click Lưu
+3. Admin B click Lưu</t>
         </is>
       </c>
       <c r="E255" s="685" t="inlineStr">
         <is>
-          <t>- Admin A tạo thành công
-- Admin B nhận lỗi "Mã gói đã được sử dụng"</t>
+          <t>2. Admin A tạo gói cước thành công
+3. Admin B nhận lỗi inline "Mã gói đã được sử dụng", không tạo gói</t>
         </is>
       </c>
       <c r="F255" s="683" t="n"/>
@@ -13296,7 +13316,7 @@
       </c>
       <c r="E256" s="685" t="inlineStr">
         <is>
-          <t>Không cho phép lưu, hiển thị thông báo lỗi</t>
+          <t>2. Không cho phép lưu, hiển thị thông báo lỗi</t>
         </is>
       </c>
       <c r="F256" s="683" t="n"/>
@@ -13339,7 +13359,7 @@
       </c>
       <c r="E257" s="685" t="inlineStr">
         <is>
-          <t>Bị chặn truy cập</t>
+          <t>1. Bị chặn truy cập</t>
         </is>
       </c>
       <c r="F257" s="683" t="n"/>
